--- a/設計書.xlsx
+++ b/設計書.xlsx
@@ -8,21 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ikura\次世代開発\ソース\IrCenser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E51338-5E6C-4A07-BFE8-26B227FB1AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309E3086-62F5-4BCA-9ECD-59D8C45BDC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="赤外線カウンター" sheetId="5" r:id="rId1"/>
-    <sheet name="赤外線センサー" sheetId="1" r:id="rId2"/>
-    <sheet name="コンデンサー" sheetId="4" r:id="rId3"/>
-    <sheet name="スイッチボタン" sheetId="2" r:id="rId4"/>
-    <sheet name="ラズパイPicoW" sheetId="3" r:id="rId5"/>
+    <sheet name="基板への設置" sheetId="6" r:id="rId1"/>
+    <sheet name="赤外線カウンター" sheetId="5" r:id="rId2"/>
+    <sheet name="赤外線センサー" sheetId="1" r:id="rId3"/>
+    <sheet name="コンデンサー" sheetId="4" r:id="rId4"/>
+    <sheet name="スイッチボタン" sheetId="2" r:id="rId5"/>
+    <sheet name="ラズパイPicoW" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -152,7 +164,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,8 +191,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -190,8 +214,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -199,20 +265,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFEB8989"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -225,6 +335,2119 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>13606</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>217714</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="7" name="グループ化 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEFF607E-D5DF-67B8-34F2-EA35CCC4A521}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10953750" y="979715"/>
+          <a:ext cx="1204231" cy="1619249"/>
+          <a:chOff x="11756571" y="1741715"/>
+          <a:chExt cx="1238249" cy="1660070"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="3" name="テキスト ボックス 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E8082A1-0EC7-9AC4-D017-CEAE7F82605D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12015107" y="3129643"/>
+            <a:ext cx="217714" cy="272142"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="テキスト ボックス 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B345B9DF-0EAA-6731-ABF6-4554117E0942}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12504965" y="3129643"/>
+            <a:ext cx="217714" cy="272142"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="テキスト ボックス 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9313A39F-0F2C-71A3-840D-4DC401EE336A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12504965" y="1741715"/>
+            <a:ext cx="217714" cy="272142"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="テキスト ボックス 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AF80EF1-7A6C-4131-395A-0C4671D4591A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12015108" y="1741715"/>
+            <a:ext cx="217714" cy="272142"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="テキスト ボックス 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10ACDDC6-0F55-9252-22AD-B39298705021}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11756571" y="1959429"/>
+            <a:ext cx="1238249" cy="1211035"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>235404</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>61232</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>170089</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCC4AEC7-1201-28EE-58FE-89592539FA4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="10774136" y="4048125"/>
+          <a:ext cx="1061357" cy="231321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Ω</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>129267</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>46263</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>42183</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EF93E3D-9661-0CBD-0D8B-BF3AD9FB2B3C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="367392" y="1236888"/>
+          <a:ext cx="489858" cy="710295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EB8989"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>LED</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>176892</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>8164</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4083</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CD48005-8B87-9D93-D3A8-5D5109CFEED0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="415017" y="2151289"/>
+          <a:ext cx="489858" cy="710294"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>コンデンサ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>11504</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>50470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>37482</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>46388</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{892C1B28-612E-A540-34E6-FDE5898E5728}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="964004" y="1241095"/>
+          <a:ext cx="502228" cy="710293"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EB8989"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>LED</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>204107</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55452F9F-A16B-424F-42A1-A1138B73C041}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7470321" y="5905500"/>
+          <a:ext cx="0" cy="1156607"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>149678</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>149678</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>204107</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="直線コネクタ 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AC0CB7F-ECD9-5A14-F995-50D6F8909EC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7007678" y="5905500"/>
+          <a:ext cx="0" cy="1156607"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>122463</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>122463</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>204107</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線コネクタ 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69CA8022-07E0-E034-79AF-BB03B6825354}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8205106" y="5905500"/>
+          <a:ext cx="0" cy="1156607"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>136071</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>122465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>122465</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="直線コネクタ 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D2878DE-27E0-78FF-124B-6E5AC032123B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7994196" y="6075590"/>
+          <a:ext cx="3292929" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>99331</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>170089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>112940</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>122465</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EB4C7B6-4234-38F1-B26A-D3691387C9D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="11291206" y="4694464"/>
+          <a:ext cx="13609" cy="1381126"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>112940</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>61232</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="直線コネクタ 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E070AA-A0F4-4615-CAA8-C2B15372EF05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="8" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="11304815" y="3258911"/>
+          <a:ext cx="9524" cy="374196"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>155121</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>146957</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>155121</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="直線コネクタ 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FE02561-F20C-3598-270E-084421253D1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11823246" y="1099457"/>
+          <a:ext cx="0" cy="615043"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>137433</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>149679</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>137433</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="直線コネクタ 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{666284FD-B849-B4A6-ADE5-93944C7C2ACA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8486775" y="1089933"/>
+          <a:ext cx="3331029" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>144236</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>145597</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>144236</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="直線コネクタ 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58A69983-114D-E1FB-FF23-68EBC4B7AC8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8478611" y="1098097"/>
+          <a:ext cx="0" cy="2664278"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>115661</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>122465</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>61233</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="直線コネクタ 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8F66B5C-C4F3-82CF-887E-FE007A82C201}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11314339" y="1544411"/>
+          <a:ext cx="1" cy="183697"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>126546</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>126546</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="44" name="直線コネクタ 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B0DCAA5-5C6F-070C-1F1F-2FF1410EFF93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8924925" y="1555296"/>
+          <a:ext cx="2389414" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>115661</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="直線コネクタ 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7351ABA9-88AC-C94D-CEAC-269CFED67C38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8933089" y="1544411"/>
+          <a:ext cx="1361" cy="2265589"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>234042</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>236763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>232683</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="正方形/長方形 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9D92489-7D4B-D668-AF3F-4D15BF78CE13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7139667" y="1427388"/>
+          <a:ext cx="489858" cy="710295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>LED</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>234042</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>236763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>232683</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="正方形/長方形 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BF6EE24-716E-0B3F-3205-381A2913A7D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5949042" y="1427388"/>
+          <a:ext cx="489858" cy="710295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>LED</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>125186</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>125186</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="57" name="直線コネクタ 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAC6C86C-87C6-483B-6B39-B7E11C21047C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6078311" y="2181225"/>
+          <a:ext cx="0" cy="1581150"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>106136</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>106136</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="直線コネクタ 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{394590FD-2CAE-9A94-9111-60655A044236}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7249886" y="2181225"/>
+          <a:ext cx="0" cy="1581150"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>115661</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>115661</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="直線コネクタ 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D07DF9E6-8F69-B1AB-AAA5-7BE32A580902}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7497536" y="2181225"/>
+          <a:ext cx="0" cy="1581150"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>6804</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>80282</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>189139</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="正方形/長方形 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15DE0903-534B-50F8-5ACD-308B293FCA82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="6973661" y="2876550"/>
+          <a:ext cx="1061357" cy="231321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Ω</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>144236</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>144236</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="直線コネクタ 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D9612C1-060F-CC45-74E7-D800FE16A93E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6335486" y="2181225"/>
+          <a:ext cx="0" cy="1581150"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>6804</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>80282</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>189139</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="正方形/長方形 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E83CF354-C786-8CD4-7C37-A95B8FF23B69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="5783036" y="2876550"/>
+          <a:ext cx="1061357" cy="231321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Ω</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>234042</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>8164</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>4083</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="正方形/長方形 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F79243E-A355-01CF-F4F6-C1E8122BDBD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7377792" y="7390039"/>
+          <a:ext cx="489858" cy="710294"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>コンデンサ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>144066</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>114130</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="63" name="直線コネクタ 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54FE5910-A368-7F2C-F4AA-ED15EE83AE3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7287816" y="7267575"/>
+          <a:ext cx="208189" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>112939</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="66" name="直線コネクタ 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B6A5406-E06C-C708-5561-DF23F1A703CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7762875" y="7258050"/>
+          <a:ext cx="208189" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="67" name="直線コネクタ 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7ED0FEF2-8197-0C3E-F2BA-2D4D49E754F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7258050" y="7143750"/>
+          <a:ext cx="9525" cy="142875"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="70" name="直線コネクタ 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CFCF37E-0108-D306-2274-473F36CA2D46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7991475" y="7143750"/>
+          <a:ext cx="9525" cy="142875"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="71" name="直線コネクタ 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{505D3B5A-C549-E414-1598-D1F68024D740}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7753350" y="7239000"/>
+          <a:ext cx="9525" cy="142875"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>127397</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>136922</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="72" name="直線コネクタ 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AADE994-B1F0-038E-9385-792A548010A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7509272" y="7262813"/>
+          <a:ext cx="9525" cy="142875"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -330,7 +2553,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -500,7 +2723,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -549,7 +2772,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -598,7 +2821,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -915,6 +3138,2355 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{547FF732-306D-454A-BAF8-775A76F8A975}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BC34"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="3.125" style="3" customWidth="1"/>
+    <col min="2" max="55" width="3.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:55" s="3" customFormat="1">
+      <c r="B1" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3">
+        <f>+B1+1</f>
+        <v>2</v>
+      </c>
+      <c r="D1" s="3">
+        <f t="shared" ref="D1:BC1" si="0">+C1+1</f>
+        <v>3</v>
+      </c>
+      <c r="E1" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F1" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G1" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H1" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="I1" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="J1" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="K1" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L1" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="M1" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="N1" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="O1" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="P1" s="3">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R1" s="3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="S1" s="3">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="T1" s="3">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U1" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="V1" s="3">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="W1" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="X1" s="3">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Y1" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="Z1" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AA1" s="3">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AB1" s="3">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AC1" s="3">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AD1" s="3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AE1" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AF1" s="3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AG1" s="3">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="AH1" s="3">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="AI1" s="3">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="3">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="AK1" s="3">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="AL1" s="3">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="AM1" s="3">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="AN1" s="3">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="AO1" s="3">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="AP1" s="3">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="AR1" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="AS1" s="3">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="AT1" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="AU1" s="3">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="AV1" s="3">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="AW1" s="3">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="AX1" s="3">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="AY1" s="3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="3">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="BA1" s="3">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="BB1" s="3">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="BC1" s="3">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="4"/>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
+      <c r="AP2" s="4"/>
+      <c r="AQ2" s="4"/>
+      <c r="AR2" s="4"/>
+      <c r="AS2" s="4"/>
+      <c r="AT2" s="4"/>
+      <c r="AU2" s="4"/>
+      <c r="AV2" s="4"/>
+      <c r="AW2" s="4"/>
+      <c r="AX2" s="4"/>
+      <c r="AY2" s="4"/>
+      <c r="AZ2" s="4"/>
+      <c r="BA2" s="4"/>
+      <c r="BB2" s="4"/>
+      <c r="BC2" s="4"/>
+    </row>
+    <row r="3" spans="1:55">
+      <c r="A3" s="3">
+        <f>+A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
+      <c r="AL3" s="4"/>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="4"/>
+      <c r="AR3" s="4"/>
+      <c r="AS3" s="4"/>
+      <c r="AT3" s="4"/>
+      <c r="AU3" s="4"/>
+      <c r="AV3" s="4"/>
+      <c r="AW3" s="4"/>
+      <c r="AX3" s="4"/>
+      <c r="AY3" s="4"/>
+      <c r="AZ3" s="4"/>
+      <c r="BA3" s="4"/>
+      <c r="BB3" s="4"/>
+      <c r="BC3" s="4"/>
+    </row>
+    <row r="4" spans="1:55">
+      <c r="A4" s="3">
+        <f t="shared" ref="A4:A34" si="1">+A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4"/>
+      <c r="AH4" s="4"/>
+      <c r="AI4" s="4"/>
+      <c r="AJ4" s="4"/>
+      <c r="AK4" s="4"/>
+      <c r="AL4" s="4"/>
+      <c r="AM4" s="4"/>
+      <c r="AN4" s="4"/>
+      <c r="AO4" s="4"/>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="4"/>
+      <c r="AR4" s="4"/>
+      <c r="AS4" s="4"/>
+      <c r="AT4" s="4"/>
+      <c r="AU4" s="4"/>
+      <c r="AV4" s="4"/>
+      <c r="AW4" s="4"/>
+      <c r="AX4" s="4"/>
+      <c r="AY4" s="4"/>
+      <c r="AZ4" s="4"/>
+      <c r="BA4" s="4"/>
+      <c r="BB4" s="4"/>
+      <c r="BC4" s="4"/>
+    </row>
+    <row r="5" spans="1:55">
+      <c r="A5" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="4"/>
+      <c r="AH5" s="4"/>
+      <c r="AI5" s="4"/>
+      <c r="AJ5" s="4"/>
+      <c r="AK5" s="4"/>
+      <c r="AL5" s="4"/>
+      <c r="AM5" s="4"/>
+      <c r="AN5" s="4"/>
+      <c r="AO5" s="4"/>
+      <c r="AP5" s="4"/>
+      <c r="AQ5" s="4"/>
+      <c r="AR5" s="4"/>
+      <c r="AS5" s="4"/>
+      <c r="AT5" s="4"/>
+      <c r="AU5" s="4"/>
+      <c r="AV5" s="4"/>
+      <c r="AW5" s="4"/>
+      <c r="AX5" s="4"/>
+      <c r="AY5" s="4"/>
+      <c r="AZ5" s="4"/>
+      <c r="BA5" s="4"/>
+      <c r="BB5" s="4"/>
+      <c r="BC5" s="4"/>
+    </row>
+    <row r="6" spans="1:55">
+      <c r="A6" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
+      <c r="AH6" s="4"/>
+      <c r="AI6" s="4"/>
+      <c r="AJ6" s="4"/>
+      <c r="AK6" s="4"/>
+      <c r="AL6" s="4"/>
+      <c r="AM6" s="4"/>
+      <c r="AN6" s="4"/>
+      <c r="AO6" s="4"/>
+      <c r="AP6" s="4"/>
+      <c r="AQ6" s="4"/>
+      <c r="AR6" s="4"/>
+      <c r="AS6" s="4"/>
+      <c r="AT6" s="4"/>
+      <c r="AU6" s="4"/>
+      <c r="AV6" s="4"/>
+      <c r="AW6" s="4"/>
+      <c r="AX6" s="4"/>
+      <c r="AY6" s="4"/>
+      <c r="AZ6" s="4"/>
+      <c r="BA6" s="4"/>
+      <c r="BB6" s="4"/>
+      <c r="BC6" s="4"/>
+    </row>
+    <row r="7" spans="1:55">
+      <c r="A7" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="4"/>
+      <c r="AC7" s="4"/>
+      <c r="AD7" s="4"/>
+      <c r="AE7" s="4"/>
+      <c r="AF7" s="4"/>
+      <c r="AG7" s="4"/>
+      <c r="AH7" s="4"/>
+      <c r="AI7" s="4"/>
+      <c r="AJ7" s="4"/>
+      <c r="AK7" s="4"/>
+      <c r="AL7" s="4"/>
+      <c r="AM7" s="4"/>
+      <c r="AN7" s="4"/>
+      <c r="AO7" s="4"/>
+      <c r="AP7" s="4"/>
+      <c r="AQ7" s="4"/>
+      <c r="AR7" s="4"/>
+      <c r="AS7" s="4"/>
+      <c r="AT7" s="4"/>
+      <c r="AU7" s="4"/>
+      <c r="AV7" s="4"/>
+      <c r="AW7" s="4"/>
+      <c r="AX7" s="4"/>
+      <c r="AY7" s="4"/>
+      <c r="AZ7" s="4"/>
+      <c r="BA7" s="4"/>
+      <c r="BB7" s="4"/>
+      <c r="BC7" s="4"/>
+    </row>
+    <row r="8" spans="1:55">
+      <c r="A8" s="3">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AH8" s="4"/>
+      <c r="AI8" s="4"/>
+      <c r="AJ8" s="4"/>
+      <c r="AK8" s="4"/>
+      <c r="AL8" s="4"/>
+      <c r="AM8" s="4"/>
+      <c r="AN8" s="4"/>
+      <c r="AO8" s="4"/>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="4"/>
+      <c r="AR8" s="4"/>
+      <c r="AS8" s="4"/>
+      <c r="AT8" s="4"/>
+      <c r="AU8" s="4"/>
+      <c r="AV8" s="4"/>
+      <c r="AW8" s="4"/>
+      <c r="AX8" s="4"/>
+      <c r="AY8" s="4"/>
+      <c r="AZ8" s="4"/>
+      <c r="BA8" s="4"/>
+      <c r="BB8" s="4"/>
+      <c r="BC8" s="4"/>
+    </row>
+    <row r="9" spans="1:55">
+      <c r="A9" s="3">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="4"/>
+      <c r="AG9" s="4"/>
+      <c r="AH9" s="4"/>
+      <c r="AI9" s="4"/>
+      <c r="AJ9" s="4"/>
+      <c r="AK9" s="4"/>
+      <c r="AL9" s="4"/>
+      <c r="AM9" s="4"/>
+      <c r="AN9" s="4"/>
+      <c r="AO9" s="4"/>
+      <c r="AP9" s="4"/>
+      <c r="AQ9" s="4"/>
+      <c r="AR9" s="4"/>
+      <c r="AS9" s="4"/>
+      <c r="AT9" s="4"/>
+      <c r="AU9" s="4"/>
+      <c r="AV9" s="4"/>
+      <c r="AW9" s="4"/>
+      <c r="AX9" s="4"/>
+      <c r="AY9" s="4"/>
+      <c r="AZ9" s="4"/>
+      <c r="BA9" s="4"/>
+      <c r="BB9" s="4"/>
+      <c r="BC9" s="4"/>
+    </row>
+    <row r="10" spans="1:55">
+      <c r="A10" s="3">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="4"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4"/>
+      <c r="AF10" s="4"/>
+      <c r="AG10" s="4"/>
+      <c r="AH10" s="4"/>
+      <c r="AI10" s="4"/>
+      <c r="AJ10" s="4"/>
+      <c r="AK10" s="4"/>
+      <c r="AL10" s="4"/>
+      <c r="AM10" s="4"/>
+      <c r="AN10" s="4"/>
+      <c r="AO10" s="4"/>
+      <c r="AP10" s="4"/>
+      <c r="AQ10" s="4"/>
+      <c r="AR10" s="4"/>
+      <c r="AS10" s="4"/>
+      <c r="AT10" s="4"/>
+      <c r="AU10" s="4"/>
+      <c r="AV10" s="4"/>
+      <c r="AW10" s="4"/>
+      <c r="AX10" s="4"/>
+      <c r="AY10" s="4"/>
+      <c r="AZ10" s="4"/>
+      <c r="BA10" s="4"/>
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="4"/>
+    </row>
+    <row r="11" spans="1:55">
+      <c r="A11" s="3">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4"/>
+      <c r="AI11" s="4"/>
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="4"/>
+      <c r="AM11" s="4"/>
+      <c r="AN11" s="4"/>
+      <c r="AO11" s="4"/>
+      <c r="AP11" s="4"/>
+      <c r="AQ11" s="4"/>
+      <c r="AR11" s="4"/>
+      <c r="AS11" s="4"/>
+      <c r="AT11" s="4"/>
+      <c r="AU11" s="4"/>
+      <c r="AV11" s="4"/>
+      <c r="AW11" s="4"/>
+      <c r="AX11" s="4"/>
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="4"/>
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="4"/>
+    </row>
+    <row r="12" spans="1:55">
+      <c r="A12" s="3">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4"/>
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="4"/>
+      <c r="AM12" s="4"/>
+      <c r="AN12" s="4"/>
+      <c r="AO12" s="4"/>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="4"/>
+      <c r="AR12" s="4"/>
+      <c r="AS12" s="4"/>
+      <c r="AT12" s="4"/>
+      <c r="AU12" s="4"/>
+      <c r="AV12" s="4"/>
+      <c r="AW12" s="4"/>
+      <c r="AX12" s="4"/>
+      <c r="AY12" s="4"/>
+      <c r="AZ12" s="4"/>
+      <c r="BA12" s="4"/>
+      <c r="BB12" s="4"/>
+      <c r="BC12" s="4"/>
+    </row>
+    <row r="13" spans="1:55">
+      <c r="A13" s="3">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="4"/>
+      <c r="AE13" s="4"/>
+      <c r="AF13" s="4"/>
+      <c r="AG13" s="4"/>
+      <c r="AH13" s="4"/>
+      <c r="AI13" s="4"/>
+      <c r="AJ13" s="4"/>
+      <c r="AK13" s="4"/>
+      <c r="AL13" s="4"/>
+      <c r="AM13" s="4"/>
+      <c r="AN13" s="4"/>
+      <c r="AO13" s="4"/>
+      <c r="AP13" s="4"/>
+      <c r="AQ13" s="4"/>
+      <c r="AR13" s="4"/>
+      <c r="AS13" s="4"/>
+      <c r="AT13" s="4"/>
+      <c r="AU13" s="4"/>
+      <c r="AV13" s="4"/>
+      <c r="AW13" s="4"/>
+      <c r="AX13" s="4"/>
+      <c r="AY13" s="4"/>
+      <c r="AZ13" s="4"/>
+      <c r="BA13" s="4"/>
+      <c r="BB13" s="4"/>
+      <c r="BC13" s="4"/>
+    </row>
+    <row r="14" spans="1:55">
+      <c r="A14" s="3">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="5">
+        <v>15</v>
+      </c>
+      <c r="T14" s="5">
+        <v>14</v>
+      </c>
+      <c r="U14" s="6"/>
+      <c r="V14" s="5">
+        <v>13</v>
+      </c>
+      <c r="W14" s="5">
+        <v>12</v>
+      </c>
+      <c r="X14" s="5">
+        <v>11</v>
+      </c>
+      <c r="Y14" s="5">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="5">
+        <v>9</v>
+      </c>
+      <c r="AB14" s="5">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="5">
+        <v>7</v>
+      </c>
+      <c r="AD14" s="5">
+        <v>6</v>
+      </c>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="5">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="5">
+        <v>4</v>
+      </c>
+      <c r="AH14" s="5">
+        <v>3</v>
+      </c>
+      <c r="AI14" s="5">
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="5">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="4"/>
+      <c r="AN14" s="4"/>
+      <c r="AO14" s="4"/>
+      <c r="AP14" s="4"/>
+      <c r="AQ14" s="4"/>
+      <c r="AR14" s="4"/>
+      <c r="AS14" s="4"/>
+      <c r="AT14" s="4"/>
+      <c r="AU14" s="4"/>
+      <c r="AV14" s="4"/>
+      <c r="AW14" s="4"/>
+      <c r="AX14" s="4"/>
+      <c r="AY14" s="4"/>
+      <c r="AZ14" s="4"/>
+      <c r="BA14" s="4"/>
+      <c r="BB14" s="4"/>
+      <c r="BC14" s="4"/>
+    </row>
+    <row r="15" spans="1:55">
+      <c r="A15" s="3">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="7">
+        <v>20</v>
+      </c>
+      <c r="T15" s="7">
+        <v>19</v>
+      </c>
+      <c r="U15" s="7">
+        <v>18</v>
+      </c>
+      <c r="V15" s="7">
+        <v>17</v>
+      </c>
+      <c r="W15" s="7">
+        <v>16</v>
+      </c>
+      <c r="X15" s="7">
+        <v>15</v>
+      </c>
+      <c r="Y15" s="7">
+        <v>14</v>
+      </c>
+      <c r="Z15" s="7">
+        <v>13</v>
+      </c>
+      <c r="AA15" s="7">
+        <v>12</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>11</v>
+      </c>
+      <c r="AC15" s="5">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="5">
+        <v>9</v>
+      </c>
+      <c r="AE15" s="5">
+        <v>8</v>
+      </c>
+      <c r="AF15" s="5">
+        <v>7</v>
+      </c>
+      <c r="AG15" s="5">
+        <v>6</v>
+      </c>
+      <c r="AH15" s="5">
+        <v>5</v>
+      </c>
+      <c r="AI15" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ15" s="5">
+        <v>3</v>
+      </c>
+      <c r="AK15" s="5">
+        <v>2</v>
+      </c>
+      <c r="AL15" s="5">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="4"/>
+      <c r="AN15" s="4"/>
+      <c r="AO15" s="4"/>
+      <c r="AP15" s="4"/>
+      <c r="AQ15" s="4"/>
+      <c r="AR15" s="4"/>
+      <c r="AS15" s="4"/>
+      <c r="AT15" s="4"/>
+      <c r="AU15" s="4"/>
+      <c r="AV15" s="4"/>
+      <c r="AW15" s="4"/>
+      <c r="AX15" s="4"/>
+      <c r="AY15" s="4"/>
+      <c r="AZ15" s="4"/>
+      <c r="BA15" s="4"/>
+      <c r="BB15" s="4"/>
+      <c r="BC15" s="4"/>
+    </row>
+    <row r="16" spans="1:55">
+      <c r="A16" s="3">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="7"/>
+      <c r="AJ16" s="7"/>
+      <c r="AK16" s="7"/>
+      <c r="AL16" s="7"/>
+      <c r="AM16" s="4"/>
+      <c r="AN16" s="4"/>
+      <c r="AO16" s="4"/>
+      <c r="AP16" s="4"/>
+      <c r="AQ16" s="4"/>
+      <c r="AR16" s="4"/>
+      <c r="AS16" s="4"/>
+      <c r="AT16" s="4"/>
+      <c r="AU16" s="4"/>
+      <c r="AV16" s="4"/>
+      <c r="AW16" s="4"/>
+      <c r="AX16" s="4"/>
+      <c r="AY16" s="4"/>
+      <c r="AZ16" s="4"/>
+      <c r="BA16" s="4"/>
+      <c r="BB16" s="4"/>
+      <c r="BC16" s="4"/>
+    </row>
+    <row r="17" spans="1:55">
+      <c r="A17" s="3">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="7"/>
+      <c r="AF17" s="7"/>
+      <c r="AG17" s="7"/>
+      <c r="AH17" s="7"/>
+      <c r="AI17" s="7"/>
+      <c r="AJ17" s="7"/>
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="8"/>
+      <c r="AN17" s="4"/>
+      <c r="AO17" s="4"/>
+      <c r="AP17" s="4"/>
+      <c r="AQ17" s="4"/>
+      <c r="AR17" s="4"/>
+      <c r="AS17" s="4"/>
+      <c r="AT17" s="4"/>
+      <c r="AU17" s="4"/>
+      <c r="AV17" s="4"/>
+      <c r="AW17" s="4"/>
+      <c r="AX17" s="4"/>
+      <c r="AY17" s="4"/>
+      <c r="AZ17" s="4"/>
+      <c r="BA17" s="4"/>
+      <c r="BB17" s="4"/>
+      <c r="BC17" s="4"/>
+    </row>
+    <row r="18" spans="1:55">
+      <c r="A18" s="3">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7"/>
+      <c r="AH18" s="7"/>
+      <c r="AI18" s="7"/>
+      <c r="AJ18" s="7"/>
+      <c r="AK18" s="8"/>
+      <c r="AL18" s="8"/>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="4"/>
+      <c r="AO18" s="4"/>
+      <c r="AP18" s="4"/>
+      <c r="AQ18" s="4"/>
+      <c r="AR18" s="4"/>
+      <c r="AS18" s="4"/>
+      <c r="AT18" s="4"/>
+      <c r="AU18" s="4"/>
+      <c r="AV18" s="4"/>
+      <c r="AW18" s="4"/>
+      <c r="AX18" s="4"/>
+      <c r="AY18" s="4"/>
+      <c r="AZ18" s="4"/>
+      <c r="BA18" s="4"/>
+      <c r="BB18" s="4"/>
+      <c r="BC18" s="4"/>
+    </row>
+    <row r="19" spans="1:55">
+      <c r="A19" s="3">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="7"/>
+      <c r="AF19" s="7"/>
+      <c r="AG19" s="7"/>
+      <c r="AH19" s="7"/>
+      <c r="AI19" s="7"/>
+      <c r="AJ19" s="7"/>
+      <c r="AK19" s="7"/>
+      <c r="AL19" s="7"/>
+      <c r="AM19" s="4"/>
+      <c r="AN19" s="4"/>
+      <c r="AO19" s="4"/>
+      <c r="AP19" s="4"/>
+      <c r="AQ19" s="4"/>
+      <c r="AR19" s="4"/>
+      <c r="AS19" s="4"/>
+      <c r="AT19" s="4"/>
+      <c r="AU19" s="4"/>
+      <c r="AV19" s="4"/>
+      <c r="AW19" s="4"/>
+      <c r="AX19" s="4"/>
+      <c r="AY19" s="4"/>
+      <c r="AZ19" s="4"/>
+      <c r="BA19" s="4"/>
+      <c r="BB19" s="4"/>
+      <c r="BC19" s="4"/>
+    </row>
+    <row r="20" spans="1:55">
+      <c r="A20" s="3">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="7">
+        <v>20</v>
+      </c>
+      <c r="T20" s="7">
+        <v>19</v>
+      </c>
+      <c r="U20" s="7">
+        <v>18</v>
+      </c>
+      <c r="V20" s="7">
+        <v>17</v>
+      </c>
+      <c r="W20" s="7">
+        <v>16</v>
+      </c>
+      <c r="X20" s="7">
+        <v>15</v>
+      </c>
+      <c r="Y20" s="7">
+        <v>14</v>
+      </c>
+      <c r="Z20" s="7">
+        <v>13</v>
+      </c>
+      <c r="AA20" s="7">
+        <v>12</v>
+      </c>
+      <c r="AB20" s="7">
+        <v>11</v>
+      </c>
+      <c r="AC20" s="5">
+        <v>10</v>
+      </c>
+      <c r="AD20" s="5">
+        <v>9</v>
+      </c>
+      <c r="AE20" s="5">
+        <v>8</v>
+      </c>
+      <c r="AF20" s="5">
+        <v>7</v>
+      </c>
+      <c r="AG20" s="5">
+        <v>6</v>
+      </c>
+      <c r="AH20" s="5">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="5">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="5">
+        <v>3</v>
+      </c>
+      <c r="AK20" s="5">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="5">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="4"/>
+      <c r="AN20" s="4"/>
+      <c r="AO20" s="4"/>
+      <c r="AP20" s="4"/>
+      <c r="AQ20" s="4"/>
+      <c r="AR20" s="4"/>
+      <c r="AS20" s="4"/>
+      <c r="AT20" s="4"/>
+      <c r="AU20" s="4"/>
+      <c r="AV20" s="4"/>
+      <c r="AW20" s="4"/>
+      <c r="AX20" s="4"/>
+      <c r="AY20" s="4"/>
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="4"/>
+      <c r="BB20" s="4"/>
+      <c r="BC20" s="4"/>
+    </row>
+    <row r="21" spans="1:55">
+      <c r="A21" s="3">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="5">
+        <v>16</v>
+      </c>
+      <c r="T21" s="5">
+        <v>17</v>
+      </c>
+      <c r="U21" s="6"/>
+      <c r="V21" s="5">
+        <v>18</v>
+      </c>
+      <c r="W21" s="5">
+        <v>19</v>
+      </c>
+      <c r="X21" s="5">
+        <v>20</v>
+      </c>
+      <c r="Y21" s="5">
+        <v>21</v>
+      </c>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="5">
+        <v>22</v>
+      </c>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="9">
+        <v>26</v>
+      </c>
+      <c r="AD21" s="10">
+        <v>27</v>
+      </c>
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="5">
+        <v>28</v>
+      </c>
+      <c r="AG21" s="5"/>
+      <c r="AH21" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="AI21" s="5"/>
+      <c r="AJ21" s="6"/>
+      <c r="AK21" s="5"/>
+      <c r="AL21" s="5"/>
+      <c r="AM21" s="4"/>
+      <c r="AN21" s="4"/>
+      <c r="AO21" s="4"/>
+      <c r="AP21" s="4"/>
+      <c r="AQ21" s="4"/>
+      <c r="AR21" s="4"/>
+      <c r="AS21" s="4"/>
+      <c r="AT21" s="4"/>
+      <c r="AU21" s="4"/>
+      <c r="AV21" s="4"/>
+      <c r="AW21" s="4"/>
+      <c r="AX21" s="4"/>
+      <c r="AY21" s="4"/>
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="4"/>
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="4"/>
+    </row>
+    <row r="22" spans="1:55">
+      <c r="A22" s="3">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="4"/>
+      <c r="AB22" s="4"/>
+      <c r="AC22" s="4"/>
+      <c r="AD22" s="4"/>
+      <c r="AE22" s="4"/>
+      <c r="AF22" s="4"/>
+      <c r="AG22" s="4"/>
+      <c r="AH22" s="4"/>
+      <c r="AI22" s="4"/>
+      <c r="AJ22" s="4"/>
+      <c r="AK22" s="4"/>
+      <c r="AL22" s="4"/>
+      <c r="AM22" s="4"/>
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="4"/>
+      <c r="AP22" s="4"/>
+      <c r="AQ22" s="4"/>
+      <c r="AR22" s="4"/>
+      <c r="AS22" s="4"/>
+      <c r="AT22" s="4"/>
+      <c r="AU22" s="4"/>
+      <c r="AV22" s="4"/>
+      <c r="AW22" s="4"/>
+      <c r="AX22" s="4"/>
+      <c r="AY22" s="4"/>
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="4"/>
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="4"/>
+    </row>
+    <row r="23" spans="1:55">
+      <c r="A23" s="3">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="4"/>
+      <c r="AB23" s="4"/>
+      <c r="AC23" s="4"/>
+      <c r="AD23" s="4"/>
+      <c r="AE23" s="4"/>
+      <c r="AF23" s="4"/>
+      <c r="AG23" s="4"/>
+      <c r="AH23" s="4"/>
+      <c r="AI23" s="4"/>
+      <c r="AJ23" s="4"/>
+      <c r="AK23" s="4"/>
+      <c r="AL23" s="4"/>
+      <c r="AM23" s="4"/>
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="4"/>
+      <c r="AP23" s="4"/>
+      <c r="AQ23" s="4"/>
+      <c r="AR23" s="4"/>
+      <c r="AS23" s="4"/>
+      <c r="AT23" s="4"/>
+      <c r="AU23" s="4"/>
+      <c r="AV23" s="4"/>
+      <c r="AW23" s="4"/>
+      <c r="AX23" s="4"/>
+      <c r="AY23" s="4"/>
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="4"/>
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="4"/>
+    </row>
+    <row r="24" spans="1:55">
+      <c r="A24" s="3">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AF24" s="4"/>
+      <c r="AG24" s="4"/>
+      <c r="AH24" s="4"/>
+      <c r="AI24" s="4"/>
+      <c r="AJ24" s="4"/>
+      <c r="AK24" s="4"/>
+      <c r="AL24" s="4"/>
+      <c r="AM24" s="4"/>
+      <c r="AN24" s="4"/>
+      <c r="AO24" s="4"/>
+      <c r="AP24" s="4"/>
+      <c r="AQ24" s="4"/>
+      <c r="AR24" s="4"/>
+      <c r="AS24" s="4"/>
+      <c r="AT24" s="4"/>
+      <c r="AU24" s="4"/>
+      <c r="AV24" s="4"/>
+      <c r="AW24" s="4"/>
+      <c r="AX24" s="4"/>
+      <c r="AY24" s="4"/>
+      <c r="AZ24" s="4"/>
+      <c r="BA24" s="4"/>
+      <c r="BB24" s="4"/>
+      <c r="BC24" s="4"/>
+    </row>
+    <row r="25" spans="1:55">
+      <c r="A25" s="3">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AF25" s="4"/>
+      <c r="AG25" s="4"/>
+      <c r="AH25" s="4"/>
+      <c r="AI25" s="4"/>
+      <c r="AJ25" s="4"/>
+      <c r="AK25" s="4"/>
+      <c r="AL25" s="4"/>
+      <c r="AM25" s="4"/>
+      <c r="AN25" s="4"/>
+      <c r="AO25" s="4"/>
+      <c r="AP25" s="4"/>
+      <c r="AQ25" s="4"/>
+      <c r="AR25" s="4"/>
+      <c r="AS25" s="4"/>
+      <c r="AT25" s="4"/>
+      <c r="AU25" s="4"/>
+      <c r="AV25" s="4"/>
+      <c r="AW25" s="4"/>
+      <c r="AX25" s="4"/>
+      <c r="AY25" s="4"/>
+      <c r="AZ25" s="4"/>
+      <c r="BA25" s="4"/>
+      <c r="BB25" s="4"/>
+      <c r="BC25" s="4"/>
+    </row>
+    <row r="26" spans="1:55">
+      <c r="A26" s="3">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+      <c r="AF26" s="4"/>
+      <c r="AG26" s="4"/>
+      <c r="AH26" s="4"/>
+      <c r="AI26" s="4"/>
+      <c r="AJ26" s="4"/>
+      <c r="AK26" s="4"/>
+      <c r="AL26" s="4"/>
+      <c r="AM26" s="4"/>
+      <c r="AN26" s="4"/>
+      <c r="AO26" s="4"/>
+      <c r="AP26" s="4"/>
+      <c r="AQ26" s="4"/>
+      <c r="AR26" s="4"/>
+      <c r="AS26" s="4"/>
+      <c r="AT26" s="4"/>
+      <c r="AU26" s="4"/>
+      <c r="AV26" s="4"/>
+      <c r="AW26" s="4"/>
+      <c r="AX26" s="4"/>
+      <c r="AY26" s="4"/>
+      <c r="AZ26" s="4"/>
+      <c r="BA26" s="4"/>
+      <c r="BB26" s="4"/>
+      <c r="BC26" s="4"/>
+    </row>
+    <row r="27" spans="1:55">
+      <c r="A27" s="3">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
+      <c r="AB27" s="4"/>
+      <c r="AC27" s="12"/>
+      <c r="AD27" s="4"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="4"/>
+      <c r="AH27" s="14"/>
+      <c r="AI27" s="4"/>
+      <c r="AJ27" s="4"/>
+      <c r="AK27" s="4"/>
+      <c r="AL27" s="4"/>
+      <c r="AM27" s="4"/>
+      <c r="AN27" s="4"/>
+      <c r="AO27" s="4"/>
+      <c r="AP27" s="4"/>
+      <c r="AQ27" s="4"/>
+      <c r="AR27" s="4"/>
+      <c r="AS27" s="4"/>
+      <c r="AT27" s="4"/>
+      <c r="AU27" s="4"/>
+      <c r="AV27" s="4"/>
+      <c r="AW27" s="4"/>
+      <c r="AX27" s="4"/>
+      <c r="AY27" s="4"/>
+      <c r="AZ27" s="4"/>
+      <c r="BA27" s="4"/>
+      <c r="BB27" s="4"/>
+      <c r="BC27" s="4"/>
+    </row>
+    <row r="28" spans="1:55">
+      <c r="A28" s="3">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="4"/>
+      <c r="AB28" s="4"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="4"/>
+      <c r="AF28" s="4"/>
+      <c r="AG28" s="4"/>
+      <c r="AH28" s="4"/>
+      <c r="AI28" s="4"/>
+      <c r="AJ28" s="4"/>
+      <c r="AK28" s="4"/>
+      <c r="AL28" s="4"/>
+      <c r="AM28" s="4"/>
+      <c r="AN28" s="4"/>
+      <c r="AO28" s="4"/>
+      <c r="AP28" s="4"/>
+      <c r="AQ28" s="4"/>
+      <c r="AR28" s="4"/>
+      <c r="AS28" s="4"/>
+      <c r="AT28" s="4"/>
+      <c r="AU28" s="4"/>
+      <c r="AV28" s="4"/>
+      <c r="AW28" s="4"/>
+      <c r="AX28" s="4"/>
+      <c r="AY28" s="4"/>
+      <c r="AZ28" s="4"/>
+      <c r="BA28" s="4"/>
+      <c r="BB28" s="4"/>
+      <c r="BC28" s="4"/>
+    </row>
+    <row r="29" spans="1:55">
+      <c r="A29" s="3">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="4"/>
+      <c r="AC29" s="4"/>
+      <c r="AD29" s="4"/>
+      <c r="AE29" s="4"/>
+      <c r="AF29" s="4"/>
+      <c r="AG29" s="4"/>
+      <c r="AH29" s="4"/>
+      <c r="AI29" s="4"/>
+      <c r="AJ29" s="4"/>
+      <c r="AK29" s="4"/>
+      <c r="AL29" s="4"/>
+      <c r="AM29" s="4"/>
+      <c r="AN29" s="4"/>
+      <c r="AO29" s="4"/>
+      <c r="AP29" s="4"/>
+      <c r="AQ29" s="4"/>
+      <c r="AR29" s="4"/>
+      <c r="AS29" s="4"/>
+      <c r="AT29" s="4"/>
+      <c r="AU29" s="4"/>
+      <c r="AV29" s="4"/>
+      <c r="AW29" s="4"/>
+      <c r="AX29" s="4"/>
+      <c r="AY29" s="4"/>
+      <c r="AZ29" s="4"/>
+      <c r="BA29" s="4"/>
+      <c r="BB29" s="4"/>
+      <c r="BC29" s="4"/>
+    </row>
+    <row r="30" spans="1:55">
+      <c r="A30" s="3">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="4"/>
+      <c r="AC30" s="4"/>
+      <c r="AD30" s="4"/>
+      <c r="AE30" s="4"/>
+      <c r="AF30" s="4"/>
+      <c r="AG30" s="4"/>
+      <c r="AH30" s="4"/>
+      <c r="AI30" s="4"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="4"/>
+      <c r="AL30" s="4"/>
+      <c r="AM30" s="4"/>
+      <c r="AN30" s="4"/>
+      <c r="AO30" s="4"/>
+      <c r="AP30" s="4"/>
+      <c r="AQ30" s="4"/>
+      <c r="AR30" s="4"/>
+      <c r="AS30" s="4"/>
+      <c r="AT30" s="4"/>
+      <c r="AU30" s="4"/>
+      <c r="AV30" s="4"/>
+      <c r="AW30" s="4"/>
+      <c r="AX30" s="4"/>
+      <c r="AY30" s="4"/>
+      <c r="AZ30" s="4"/>
+      <c r="BA30" s="4"/>
+      <c r="BB30" s="4"/>
+      <c r="BC30" s="4"/>
+    </row>
+    <row r="31" spans="1:55">
+      <c r="A31" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="4"/>
+      <c r="AB31" s="4"/>
+      <c r="AC31" s="4"/>
+      <c r="AD31" s="4"/>
+      <c r="AE31" s="4"/>
+      <c r="AF31" s="4"/>
+      <c r="AG31" s="4"/>
+      <c r="AH31" s="4"/>
+      <c r="AI31" s="4"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
+      <c r="AM31" s="4"/>
+      <c r="AN31" s="4"/>
+      <c r="AO31" s="4"/>
+      <c r="AP31" s="4"/>
+      <c r="AQ31" s="4"/>
+      <c r="AR31" s="4"/>
+      <c r="AS31" s="4"/>
+      <c r="AT31" s="4"/>
+      <c r="AU31" s="4"/>
+      <c r="AV31" s="4"/>
+      <c r="AW31" s="4"/>
+      <c r="AX31" s="4"/>
+      <c r="AY31" s="4"/>
+      <c r="AZ31" s="4"/>
+      <c r="BA31" s="4"/>
+      <c r="BB31" s="4"/>
+      <c r="BC31" s="4"/>
+    </row>
+    <row r="32" spans="1:55">
+      <c r="A32" s="3">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
+      <c r="AB32" s="4"/>
+      <c r="AC32" s="4"/>
+      <c r="AD32" s="4"/>
+      <c r="AE32" s="4"/>
+      <c r="AF32" s="4"/>
+      <c r="AG32" s="4"/>
+      <c r="AH32" s="4"/>
+      <c r="AI32" s="4"/>
+      <c r="AJ32" s="4"/>
+      <c r="AK32" s="4"/>
+      <c r="AL32" s="4"/>
+      <c r="AM32" s="4"/>
+      <c r="AN32" s="4"/>
+      <c r="AO32" s="4"/>
+      <c r="AP32" s="4"/>
+      <c r="AQ32" s="4"/>
+      <c r="AR32" s="4"/>
+      <c r="AS32" s="4"/>
+      <c r="AT32" s="4"/>
+      <c r="AU32" s="4"/>
+      <c r="AV32" s="4"/>
+      <c r="AW32" s="4"/>
+      <c r="AX32" s="4"/>
+      <c r="AY32" s="4"/>
+      <c r="AZ32" s="4"/>
+      <c r="BA32" s="4"/>
+      <c r="BB32" s="4"/>
+      <c r="BC32" s="4"/>
+    </row>
+    <row r="33" spans="1:55">
+      <c r="A33" s="3">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="4"/>
+      <c r="AC33" s="4"/>
+      <c r="AD33" s="4"/>
+      <c r="AE33" s="4"/>
+      <c r="AF33" s="4"/>
+      <c r="AG33" s="4"/>
+      <c r="AH33" s="4"/>
+      <c r="AI33" s="4"/>
+      <c r="AJ33" s="4"/>
+      <c r="AK33" s="4"/>
+      <c r="AL33" s="4"/>
+      <c r="AM33" s="4"/>
+      <c r="AN33" s="4"/>
+      <c r="AO33" s="4"/>
+      <c r="AP33" s="4"/>
+      <c r="AQ33" s="4"/>
+      <c r="AR33" s="4"/>
+      <c r="AS33" s="4"/>
+      <c r="AT33" s="4"/>
+      <c r="AU33" s="4"/>
+      <c r="AV33" s="4"/>
+      <c r="AW33" s="4"/>
+      <c r="AX33" s="4"/>
+      <c r="AY33" s="4"/>
+      <c r="AZ33" s="4"/>
+      <c r="BA33" s="4"/>
+      <c r="BB33" s="4"/>
+      <c r="BC33" s="4"/>
+    </row>
+    <row r="34" spans="1:55">
+      <c r="A34" s="3">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="4"/>
+      <c r="W34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
+      <c r="AB34" s="4"/>
+      <c r="AC34" s="4"/>
+      <c r="AD34" s="4"/>
+      <c r="AE34" s="4"/>
+      <c r="AF34" s="4"/>
+      <c r="AG34" s="4"/>
+      <c r="AH34" s="4"/>
+      <c r="AI34" s="4"/>
+      <c r="AJ34" s="4"/>
+      <c r="AK34" s="4"/>
+      <c r="AL34" s="4"/>
+      <c r="AM34" s="4"/>
+      <c r="AN34" s="4"/>
+      <c r="AO34" s="4"/>
+      <c r="AP34" s="4"/>
+      <c r="AQ34" s="4"/>
+      <c r="AR34" s="4"/>
+      <c r="AS34" s="4"/>
+      <c r="AT34" s="4"/>
+      <c r="AU34" s="4"/>
+      <c r="AV34" s="4"/>
+      <c r="AW34" s="4"/>
+      <c r="AX34" s="4"/>
+      <c r="AY34" s="4"/>
+      <c r="AZ34" s="4"/>
+      <c r="BA34" s="4"/>
+      <c r="BB34" s="4"/>
+      <c r="BC34" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="77" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F34BC181-A555-4AB8-B4D0-2C019228AF92}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -922,51 +5494,6 @@
     <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" ht="18">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -977,13 +5504,41 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2D069B-FAFD-4C6A-A3F6-E7B5FC09B54E}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="2" customFormat="1" ht="18">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -994,13 +5549,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903B459A-9CFF-4A9F-9DE1-CBD111FCB7F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2D069B-FAFD-4C6A-A3F6-E7B5FC09B54E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1011,6 +5566,23 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903B459A-9CFF-4A9F-9DE1-CBD111FCB7F9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1" s="1" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A112CEF-4627-4FCA-8313-AB7396065842}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>

--- a/設計書.xlsx
+++ b/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ikura\次世代開発\ソース\IrCenser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309E3086-62F5-4BCA-9ECD-59D8C45BDC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD7E830-1DA4-48E7-8172-E97334CF2265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基板への設置" sheetId="6" r:id="rId1"/>
@@ -1694,10 +1694,18 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>LED</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2051,14 +2059,14 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>234042</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>8164</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>4083</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2073,8 +2081,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7377792" y="7390039"/>
-          <a:ext cx="489858" cy="710294"/>
+          <a:off x="7377792" y="5267324"/>
+          <a:ext cx="489858" cy="552451"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2103,7 +2111,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
@@ -2122,70 +2130,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>144066</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>114130</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="63" name="直線コネクタ 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54FE5910-A368-7F2C-F4AA-ED15EE83AE3E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="7287816" y="7267575"/>
-          <a:ext cx="208189" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="25400">
-          <a:headEnd type="oval"/>
-          <a:tailEnd type="oval"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>32</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>112939</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2200,7 +2154,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="7762875" y="7258050"/>
+          <a:off x="7762875" y="5991225"/>
           <a:ext cx="208189" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -2230,32 +2184,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>151039</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>151039</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="67" name="直線コネクタ 66">
+        <xdr:cNvPr id="12" name="直線コネクタ 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7ED0FEF2-8197-0C3E-F2BA-2D4D49E754F4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAB9261D-A7D3-5535-9F12-08C8EFD097FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7258050" y="7143750"/>
-          <a:ext cx="9525" cy="142875"/>
+        <a:xfrm>
+          <a:off x="7771039" y="5810250"/>
+          <a:ext cx="0" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2284,32 +2238,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="70" name="直線コネクタ 69">
+        <xdr:cNvPr id="20" name="直線コネクタ 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CFCF37E-0108-D306-2274-473F36CA2D46}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{608BD21A-4D71-5CF2-7A13-68EAF4D5C357}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7991475" y="7143750"/>
-          <a:ext cx="9525" cy="142875"/>
+        <a:xfrm flipH="1">
+          <a:off x="7277100" y="5991225"/>
+          <a:ext cx="266700" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2338,32 +2292,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>170089</xdr:colOff>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>170089</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="71" name="直線コネクタ 70">
+        <xdr:cNvPr id="22" name="直線コネクタ 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{505D3B5A-C549-E414-1598-D1F68024D740}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9E280C3-992D-434A-EDF6-544A8BB34EA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7753350" y="7239000"/>
-          <a:ext cx="9525" cy="142875"/>
+        <a:xfrm>
+          <a:off x="7551964" y="5810250"/>
+          <a:ext cx="0" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2392,56 +2346,215 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>127397</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>119063</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>114301</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>136922</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>228601</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="72" name="直線コネクタ 71">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="テキスト ボックス 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AADE994-B1F0-038E-9385-792A548010A6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9933ABC3-D729-BF1F-4798-C575420F8C0C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7509272" y="7262813"/>
-          <a:ext cx="9525" cy="142875"/>
+        <a:xfrm>
+          <a:off x="11544301" y="3238500"/>
+          <a:ext cx="590550" cy="257175"/>
         </a:xfrm>
-        <a:prstGeom prst="line">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="25400">
-          <a:headEnd type="oval"/>
-          <a:tailEnd type="oval"/>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
-    </xdr:cxnSp>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>100KΩ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>161926</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="テキスト ボックス 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{648129B3-7D0D-419E-FB83-32B8D8A9A3D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7667626" y="2133600"/>
+          <a:ext cx="590550" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>330Ω</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>161926</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="テキスト ボックス 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99528C78-0BA6-8333-F048-52B9B5681C3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6477001" y="2133600"/>
+          <a:ext cx="590550" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>330Ω</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/設計書.xlsx
+++ b/設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ikura\次世代開発\ソース\IrCenser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD7E830-1DA4-48E7-8172-E97334CF2265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E229779-3A9C-4BAD-A63A-A3F8CF215CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2513,6 +2513,324 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6477001" y="2133600"/>
+          <a:ext cx="590550" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>330Ω</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>234042</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>236763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>232683</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="正方形/長方形 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C06D782-8678-3C29-0F20-C50296EF2EC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4758417" y="713013"/>
+          <a:ext cx="489858" cy="710295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EB8989"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>LED</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>125186</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>125186</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="直線コネクタ 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A692E483-932A-3604-BEEA-776D19ED9C04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4887686" y="1466850"/>
+          <a:ext cx="0" cy="1581150"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>144236</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>144236</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="直線コネクタ 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6F21DE7-F82D-B9BD-B6D4-E9C72666F34A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5144861" y="1466850"/>
+          <a:ext cx="0" cy="1581150"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>6804</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>80282</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>189139</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="正方形/長方形 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94394456-6E60-96C9-C937-2D339382AB2F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="4592411" y="2162175"/>
+          <a:ext cx="1061357" cy="231321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Ω</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>161926</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="テキスト ボックス 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9ADC6AE-D42A-F85B-E81A-850B465CC633}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5286376" y="2133600"/>
           <a:ext cx="590550" cy="257175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/設計書.xlsx
+++ b/設計書.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ikura\次世代開発\ソース\IrCenser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E229779-3A9C-4BAD-A63A-A3F8CF215CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F18DEEA-FD3B-47A1-8E4A-25C38E64812B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基板への設置" sheetId="6" r:id="rId1"/>
-    <sheet name="赤外線カウンター" sheetId="5" r:id="rId2"/>
-    <sheet name="赤外線センサー" sheetId="1" r:id="rId3"/>
-    <sheet name="コンデンサー" sheetId="4" r:id="rId4"/>
-    <sheet name="スイッチボタン" sheetId="2" r:id="rId5"/>
-    <sheet name="ラズパイPicoW" sheetId="3" r:id="rId6"/>
+    <sheet name="距離リセット" sheetId="7" r:id="rId2"/>
+    <sheet name="赤外線カウンター" sheetId="5" r:id="rId3"/>
+    <sheet name="赤外線センサー" sheetId="1" r:id="rId4"/>
+    <sheet name="コンデンサー" sheetId="4" r:id="rId5"/>
+    <sheet name="スイッチボタン" sheetId="2" r:id="rId6"/>
+    <sheet name="ラズパイPicoW" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>赤外線センサー</t>
     <rPh sb="0" eb="3">
@@ -159,6 +160,241 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>距離リセットボタン</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>概要</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離リセットボタンを押したら、距離が０になり、その状態から距離計測を行う。</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="29" eb="33">
+      <t>キョリケイソク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設計</t>
+    <rPh sb="0" eb="2">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離リセットボタンを押したら、距離リセットテーブルへIDと距離を保存する</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離リセットテーブル</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離を算出する際に、距離リセットテーブルから該当IDの距離を取得</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サンシュツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取得した距離を、現在の距離計算の距離から引いた値とする</t>
+    <rPh sb="0" eb="2">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細設計</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラズパイからサーバへの送信文字列</t>
+    <rPh sb="11" eb="16">
+      <t>ソウシンモジレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"id" : id ,</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"dist" : 距離</t>
+    <rPh sb="9" eb="11">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離リセットの距離をリセットする機能を追加。</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離リセットのリセットボタンを押したら、該当IDの距離リセットテーブルをクリアする</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ID:1のリセットボタンをクリック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離リセット</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>距離リセットのリセット</t>
+    <rPh sb="0" eb="2">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"type" : "RstDist" ,</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"type" : "RstDistRst" ,</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"id" : id </t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -167,7 +403,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,6 +434,13 @@
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -257,7 +500,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -280,11 +523,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -312,6 +570,17 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -5918,6 +6187,277 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA1F4670-BA7C-4132-B66E-39311DA12AF5}">
+  <dimension ref="A1:P53"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="B3" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="C10" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="D13" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="16"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="D14" s="15">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="D15" s="15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15">
+        <v>13.2</v>
+      </c>
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="D16" s="15">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="18" spans="3:16">
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="3:16">
+      <c r="D20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="16"/>
+    </row>
+    <row r="21" spans="3:16">
+      <c r="D21" s="15">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="G21" s="15"/>
+    </row>
+    <row r="23" spans="3:16">
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16">
+      <c r="C25" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16">
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16">
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16">
+      <c r="D30" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="16"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="M30" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="P30" s="16"/>
+    </row>
+    <row r="31" spans="3:16">
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="G31" s="15"/>
+      <c r="I31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M31" s="15">
+        <v>1</v>
+      </c>
+      <c r="N31" s="15"/>
+      <c r="O31" s="19">
+        <v>0</v>
+      </c>
+      <c r="P31" s="19"/>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="C36" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="D38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="E40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="F41" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="F42" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="F43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="E44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="C46" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="D48" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6">
+      <c r="E50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="5:6">
+      <c r="F51" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="5:6">
+      <c r="F52" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="5:6">
+      <c r="E53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F34BC181-A555-4AB8-B4D0-2C019228AF92}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -5925,51 +6465,6 @@
     <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" ht="18">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5980,13 +6475,41 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2D069B-FAFD-4C6A-A3F6-E7B5FC09B54E}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="2" customFormat="1" ht="18">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5997,13 +6520,13 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903B459A-9CFF-4A9F-9DE1-CBD111FCB7F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2D069B-FAFD-4C6A-A3F6-E7B5FC09B54E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -6014,6 +6537,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903B459A-9CFF-4A9F-9DE1-CBD111FCB7F9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1" s="1" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A112CEF-4627-4FCA-8313-AB7396065842}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>

--- a/設計書.xlsx
+++ b/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ikura\次世代開発\ソース\IrCenser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F18DEEA-FD3B-47A1-8E4A-25C38E64812B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB987C3-4BB7-4EFD-A96C-ED03493F7C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基板への設置" sheetId="6" r:id="rId1"/>
@@ -3144,10 +3144,2935 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>13606</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>200024</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="17" name="グループ化 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C5634DA-4D31-4102-A174-8E7D4CEFB8A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2619375" y="5724525"/>
+          <a:ext cx="1204231" cy="1619249"/>
+          <a:chOff x="11756571" y="1741715"/>
+          <a:chExt cx="1238249" cy="1660070"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="18" name="テキスト ボックス 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03E5C4B0-9D40-C3DB-4B1D-B2E3BDCDC5FD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12015107" y="3129643"/>
+            <a:ext cx="217714" cy="272142"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="21" name="テキスト ボックス 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C7C14C0-B943-6BC5-A233-976634205D22}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12504965" y="3129643"/>
+            <a:ext cx="217714" cy="272142"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="32" name="テキスト ボックス 31">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02CCF2B8-8F7F-27B9-CF09-D428F9A5B473}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12504965" y="1741715"/>
+            <a:ext cx="217714" cy="272142"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="34" name="テキスト ボックス 33">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82CE27F4-D4A5-9589-029C-B13FA6D715D4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12015108" y="1741715"/>
+            <a:ext cx="217714" cy="272142"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="36" name="テキスト ボックス 35">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEC87975-23DC-C1B3-F764-A8AF81A8C780}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11756571" y="1959429"/>
+            <a:ext cx="1238249" cy="1211035"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>4082</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>234043</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>112939</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>227239</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="正方形/長方形 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BABB3CAC-A48B-4FAC-BE57-8627A9F73A95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4052207" y="7377793"/>
+          <a:ext cx="1061357" cy="231321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Ω</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>117021</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>111579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>4082</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>112940</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="38" name="直線コネクタ 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4FC8593-05F3-63F9-607F-844314E9FACD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="37" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3450771" y="7493454"/>
+          <a:ext cx="601436" cy="1361"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>112939</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>111579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>111579</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="直線コネクタ 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B808EE83-D195-B620-CD5E-9989D16719A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="37" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5113564" y="7493454"/>
+          <a:ext cx="2849336" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>121653</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>17689</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>131990</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="直線コネクタ 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1FCA69A-5835-EC37-072B-86961EB1FCDE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7979778" y="6447064"/>
+          <a:ext cx="10337" cy="1049111"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>112939</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>112939</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="50" name="直線コネクタ 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{662DA2C9-E5BA-687B-C149-A539BEB26346}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3446689" y="7286625"/>
+          <a:ext cx="0" cy="209550"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>112939</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>111579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>111579</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="直線コネクタ 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80B35066-5FF3-658B-2407-05504CC942FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3446689" y="5588454"/>
+          <a:ext cx="2877911" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>130628</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>130628</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="直線コネクタ 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C964DC-D64C-B2C1-87E6-FA7978B941E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6321878" y="5027839"/>
+          <a:ext cx="0" cy="563336"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>112939</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>112939</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="67" name="直線コネクタ 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{147AEB0E-A635-ACE4-5130-03976FCC4439}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3446689" y="5591175"/>
+          <a:ext cx="0" cy="209550"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="68" name="直線コネクタ 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA138A5E-59CA-EFAC-FA4E-F11833C994F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2979964" y="5353050"/>
+          <a:ext cx="0" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>121104</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>121104</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="70" name="直線コネクタ 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{919155CA-F7AB-DD11-9143-85572B084FA7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3000375" y="5359854"/>
+          <a:ext cx="3086100" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>121103</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>121103</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="73" name="直線コネクタ 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C001BD7D-7304-29B1-D48E-B0E858D29AD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6074228" y="5027839"/>
+          <a:ext cx="0" cy="334736"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="oval"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>200026</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>76201</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="75" name="テキスト ボックス 74">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB5F3ECE-90CF-E873-3DBE-0FAFA169F824}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4248151" y="7686675"/>
+          <a:ext cx="590550" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>100KΩ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>131860</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>142024</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>224226</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A489DD66-0233-75DE-C910-5AC1E455555C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676146" y="1752600"/>
+          <a:ext cx="1370878" cy="186126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>243689</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>245309</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>243689</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E5AD3EA-1DCA-D12E-5BE3-01804108D85E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="572861" y="3182832"/>
+          <a:ext cx="1577448" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>10261</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>8685</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>10261</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>233893</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B968B4C-0245-4DE4-3FB3-6F06628ABED7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1370975" y="1968114"/>
+          <a:ext cx="0" cy="1204922"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38275</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>204582</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>258969</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>231743</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="テキスト ボックス 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF8816CC-25E6-18B0-BCFF-FD7A5056BAD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1126846" y="2408939"/>
+          <a:ext cx="492837" cy="272090"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>10cm</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>48284</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>233996</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>20889</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>79793</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="テキスト ボックス 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4ABC79-96E4-1530-EF00-7795B436A58B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2225427" y="2193425"/>
+          <a:ext cx="1333319" cy="580582"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リセットすることで </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>-10cm </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>となる</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>161732</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>171896</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>224226</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF870792-BEA9-CD6A-D385-C6FC0700DCA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3699589" y="1752600"/>
+          <a:ext cx="1370878" cy="186126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>58447</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>243689</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>3038</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>243689</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91DD896-C758-807E-A241-4369C1C1DBD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3596304" y="3182832"/>
+          <a:ext cx="1577448" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>40131</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>8685</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>40131</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>233893</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線矢印コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3741CCE7-0F26-E1E6-EF95-303E3D732D44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4394417" y="1968114"/>
+          <a:ext cx="0" cy="1204922"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>115093</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>204582</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>265309</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>231743</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="テキスト ボックス 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94FE050D-C386-745C-D48E-6C78080AC9C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4197236" y="2408939"/>
+          <a:ext cx="422359" cy="272090"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>0cm</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171122</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>204453</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>181286</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>145650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1DAD568-A0B0-9484-66F4-0BA36C689BBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3708979" y="3633453"/>
+          <a:ext cx="1370878" cy="186126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>67836</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>165114</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>12427</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>165114</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02F483F4-8E52-7526-6FB1-529E53FB9B60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3605693" y="5063685"/>
+          <a:ext cx="1577448" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>49521</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>175039</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>49521</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>184758</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FD2C17E-D526-6EF1-8C95-6E7C100FD4A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4403807" y="3848968"/>
+          <a:ext cx="0" cy="744504"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>124093</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>69696</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="テキスト ボックス 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCA502DD-DA2C-D2BB-56DA-7B732458BD43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4543693" y="3879696"/>
+          <a:ext cx="4057381" cy="406554"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
+            <a:t>7cm</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400"/>
+            <a:t>だけど、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
+            <a:t>-10cm</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400"/>
+            <a:t>で→ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400"/>
+            <a:t>-3cm</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" baseline="0"/>
+            <a:t> → 絶対値 → </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" baseline="0"/>
+            <a:t>3cm</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>105704</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>204350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>265481</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>165114</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="直方体 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B40F12F-B1D4-CDB1-18F6-1BDBB62A409E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4187847" y="4613064"/>
+          <a:ext cx="431920" cy="450621"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>129151</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>12541</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>3143</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>39703</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="テキスト ボックス 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7CB0BBE-F127-669D-A8AB-CA1AD4E6B504}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3720076" y="4536916"/>
+          <a:ext cx="426442" cy="265287"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>3cm</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>176893</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>191134</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>95283</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="87" name="グループ化 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6C51D3D-FB38-4E79-9866-BB00ACAA8021}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="729343" y="5531304"/>
+          <a:ext cx="5814966" cy="5517729"/>
+          <a:chOff x="13786437" y="1170214"/>
+          <a:chExt cx="5729241" cy="5674211"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="88" name="テキスト ボックス 87">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDE65FFD-B775-7603-8241-24ED45DC3EC2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17480229" y="2280577"/>
+            <a:ext cx="2001830" cy="334180"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+              <a:t>17cm</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="89" name="テキスト ボックス 88">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AB6EE34-057A-8F4E-0723-43236B733472}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17502642" y="4107137"/>
+            <a:ext cx="2001830" cy="343783"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+              <a:t>14cm</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="90" name="テキスト ボックス 89">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8C2B2C2-6600-8399-E503-263DC9D808E0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17513848" y="5743195"/>
+            <a:ext cx="2001830" cy="334179"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+              <a:t>11cm</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="91" name="テキスト ボックス 90">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD4CE512-A3C6-6E21-81FF-946FA78F99F1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13786437" y="1170214"/>
+            <a:ext cx="595035" cy="435697"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600" b="1"/>
+              <a:t>現状</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="92" name="正方形/長方形 91">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26B2E437-6904-8D9B-6DC1-43B27FB9DFAF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="14257703" y="1714500"/>
+            <a:ext cx="1370530" cy="178854"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="93" name="直線コネクタ 92">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0EC9EDD-EC0E-20E8-4DF4-40E1DD4C8559}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="14151429" y="3136877"/>
+            <a:ext cx="1583079" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="25400"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="94" name="直線矢印コネクタ 93">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B33D4887-9537-D353-3BCC-4C7DE19A58F5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="14956631" y="1921594"/>
+            <a:ext cx="0" cy="1205870"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:headEnd type="triangle"/>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="95" name="テキスト ボックス 94">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7AC403C-CF51-27AC-6E69-2C3281CBBFA7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="14705437" y="2364406"/>
+            <a:ext cx="499096" cy="271065"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+              <a:t>20cm</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="96" name="正方形/長方形 95">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CA536FF-7680-CC29-A147-9CA8F7ECD0C9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16706988" y="1714500"/>
+            <a:ext cx="1370531" cy="178854"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="97" name="直線コネクタ 96">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63980DF2-F7EB-EB48-D748-BB3EE0DE7959}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16600714" y="3136878"/>
+            <a:ext cx="1583080" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="25400"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="98" name="直線矢印コネクタ 97">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AE8470C-11CD-47FA-1065-070D32F8BC6D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17405917" y="1921594"/>
+            <a:ext cx="0" cy="929502"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:headEnd type="triangle"/>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="99" name="直方体 98">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0FA829E-04AF-32E1-E722-F79FD79696EA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17284560" y="2862346"/>
+            <a:ext cx="244974" cy="256092"/>
+          </a:xfrm>
+          <a:prstGeom prst="cube">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="100" name="正方形/長方形 99">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B84027D0-D45A-8006-6D2C-916257E24A92}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16706988" y="3653119"/>
+            <a:ext cx="1370531" cy="188459"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="101" name="直線コネクタ 100">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B4D4E98-8244-1B8D-6E4F-549CD807087E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16600714" y="5085100"/>
+            <a:ext cx="1583080" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="25400"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="102" name="直線矢印コネクタ 101">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{443F3127-F238-DE0C-5940-2CF1FFC1174A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17405917" y="3869818"/>
+            <a:ext cx="0" cy="744230"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:headEnd type="triangle"/>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="103" name="直方体 102">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46E5EB11-1A42-1E1A-B20D-6B69196FC557}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17284560" y="4810569"/>
+            <a:ext cx="244974" cy="256090"/>
+          </a:xfrm>
+          <a:prstGeom prst="cube">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="104" name="直方体 103">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD478A7C-7A50-B899-297F-75D9381BE580}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17284560" y="4621669"/>
+            <a:ext cx="244974" cy="256092"/>
+          </a:xfrm>
+          <a:prstGeom prst="cube">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="105" name="正方形/長方形 104">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C234A8C-2D9F-631F-685D-70CCF78BADDB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16706988" y="5422048"/>
+            <a:ext cx="1370531" cy="178854"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="106" name="直線コネクタ 105">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{334833C9-0BD1-0924-3E5C-74887AFCE146}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16600714" y="6844425"/>
+            <a:ext cx="1583080" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="25400"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="107" name="直線矢印コネクタ 106">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B84C14A-0D9A-7364-A4C7-A62A8B6273D8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17405917" y="5638747"/>
+            <a:ext cx="0" cy="529291"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:headEnd type="triangle"/>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="108" name="直方体 107">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36594775-CE17-C88A-E80E-E4AC1B035DD5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17284560" y="6569893"/>
+            <a:ext cx="244974" cy="256091"/>
+          </a:xfrm>
+          <a:prstGeom prst="cube">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="109" name="直方体 108">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A21DB40-DBD1-D9B9-0DCE-3D2CCEE2A816}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17284560" y="6390599"/>
+            <a:ext cx="244974" cy="256091"/>
+          </a:xfrm>
+          <a:prstGeom prst="cube">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="110" name="直方体 109">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C079826-B5D8-A705-402A-483D48DCC4B0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17284560" y="6190494"/>
+            <a:ext cx="244974" cy="256091"/>
+          </a:xfrm>
+          <a:prstGeom prst="cube">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3253,7 +6178,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3423,7 +6348,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3472,7 +6397,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3521,7 +6446,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -6188,272 +9113,276 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA1F4670-BA7C-4132-B66E-39311DA12AF5}">
-  <dimension ref="A1:P53"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:3">
       <c r="B3" s="17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:3">
       <c r="C5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:3">
       <c r="C6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="B8" s="17" t="s">
+    <row r="52" spans="2:7">
+      <c r="B52" s="17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="C10" s="17" t="s">
+    <row r="54" spans="2:7">
+      <c r="C54" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="D12" t="s">
+    <row r="56" spans="2:7">
+      <c r="D56" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="D13" s="16" t="s">
+    <row r="57" spans="2:7">
+      <c r="D57" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16" t="s">
+      <c r="E57" s="16"/>
+      <c r="F57" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="16"/>
+      <c r="G57" s="16"/>
     </row>
-    <row r="14" spans="1:7">
-      <c r="D14" s="15">
+    <row r="58" spans="2:7">
+      <c r="D58" s="15">
         <v>1</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15">
+      <c r="E58" s="15"/>
+      <c r="F58" s="15">
         <v>10.5</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="G58" s="15"/>
     </row>
-    <row r="15" spans="1:7">
-      <c r="D15" s="15">
+    <row r="59" spans="2:7">
+      <c r="D59" s="15">
         <v>2</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15">
+      <c r="E59" s="15"/>
+      <c r="F59" s="15">
         <v>13.2</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G59" s="15"/>
     </row>
-    <row r="16" spans="1:7">
-      <c r="D16" s="15">
+    <row r="60" spans="2:7">
+      <c r="D60" s="15">
         <v>3</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15">
+      <c r="E60" s="15"/>
+      <c r="F60" s="15">
         <v>10.199999999999999</v>
       </c>
-      <c r="G16" s="15"/>
+      <c r="G60" s="15"/>
     </row>
-    <row r="18" spans="3:16">
-      <c r="D18" t="s">
+    <row r="62" spans="2:7">
+      <c r="D62" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="3:16">
-      <c r="D20" s="16" t="s">
+    <row r="64" spans="2:7">
+      <c r="D64" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16" t="s">
+      <c r="E64" s="16"/>
+      <c r="F64" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="16"/>
+      <c r="G64" s="16"/>
     </row>
-    <row r="21" spans="3:16">
-      <c r="D21" s="15">
+    <row r="65" spans="2:16">
+      <c r="D65" s="15">
         <v>1</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15">
+      <c r="E65" s="15"/>
+      <c r="F65" s="15">
         <v>10.5</v>
       </c>
-      <c r="G21" s="15"/>
+      <c r="G65" s="15"/>
     </row>
-    <row r="23" spans="3:16">
-      <c r="D23" t="s">
+    <row r="67" spans="2:16">
+      <c r="D67" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="3:16">
-      <c r="C25" s="17" t="s">
+    <row r="69" spans="2:16">
+      <c r="C69" s="17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="3:16">
-      <c r="D27" t="s">
+    <row r="71" spans="2:16">
+      <c r="D71" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="3:16">
-      <c r="D29" t="s">
+    <row r="73" spans="2:16">
+      <c r="D73" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="3:16">
-      <c r="D30" s="16" t="s">
+    <row r="74" spans="2:16">
+      <c r="D74" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16" t="s">
+      <c r="E74" s="16"/>
+      <c r="F74" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="G30" s="16"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="M30" s="16" t="s">
+      <c r="G74" s="16"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="M74" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16" t="s">
+      <c r="N74" s="16"/>
+      <c r="O74" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="P30" s="16"/>
+      <c r="P74" s="16"/>
     </row>
-    <row r="31" spans="3:16">
-      <c r="D31" s="15">
+    <row r="75" spans="2:16">
+      <c r="D75" s="15">
         <v>1</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15">
+      <c r="E75" s="15"/>
+      <c r="F75" s="15">
         <v>10.5</v>
       </c>
-      <c r="G31" s="15"/>
-      <c r="I31" s="3" t="s">
+      <c r="G75" s="15"/>
+      <c r="I75" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J75" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="K75" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M31" s="15">
+      <c r="M75" s="15">
         <v>1</v>
       </c>
-      <c r="N31" s="15"/>
-      <c r="O31" s="19">
+      <c r="N75" s="15"/>
+      <c r="O75" s="19">
         <v>0</v>
       </c>
-      <c r="P31" s="19"/>
+      <c r="P75" s="19"/>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="17" t="s">
+    <row r="78" spans="2:16">
+      <c r="B78" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="C36" s="17" t="s">
+    <row r="80" spans="2:16">
+      <c r="C80" s="17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
-      <c r="D38" t="s">
+    <row r="82" spans="3:6">
+      <c r="D82" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="E40" t="s">
+    <row r="84" spans="3:6">
+      <c r="E84" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="2:6">
-      <c r="F41" t="s">
+    <row r="85" spans="3:6">
+      <c r="F85" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="2:6">
-      <c r="F42" s="18" t="s">
+    <row r="86" spans="3:6">
+      <c r="F86" s="18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="F43" t="s">
+    <row r="87" spans="3:6">
+      <c r="F87" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="2:6">
-      <c r="E44" t="s">
+    <row r="88" spans="3:6">
+      <c r="E88" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
-      <c r="C46" s="17" t="s">
+    <row r="90" spans="3:6">
+      <c r="C90" s="17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
-      <c r="D48" t="s">
+    <row r="92" spans="3:6">
+      <c r="D92" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="5:6">
-      <c r="E50" t="s">
+    <row r="94" spans="3:6">
+      <c r="E94" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="5:6">
-      <c r="F51" t="s">
+    <row r="95" spans="3:6">
+      <c r="F95" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="5:6">
-      <c r="F52" s="18" t="s">
+    <row r="96" spans="3:6">
+      <c r="F96" s="18" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="5:6">
-      <c r="E53" t="s">
+    <row r="97" spans="5:5">
+      <c r="E97" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="M74:N74"/>
+    <mergeCell ref="O74:P74"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="26" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
